--- a/database/event/3112/event_3112_evp_summary.xlsx
+++ b/database/event/3112/event_3112_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.3781</v>
+        <v>9.768599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4355</v>
+        <v>2.5369</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3672</v>
+        <v>3.4479</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3781</v>
+        <v>9.768599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1405</v>
+        <v>5.5311</v>
       </c>
       <c r="G2" t="n">
         <v>4.2375</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7573</v>
+        <v>6.3696</v>
       </c>
       <c r="I2" t="n">
-        <v>5.811</v>
+        <v>6.4773</v>
       </c>
       <c r="J2" t="n">
         <v>4.2375</v>
@@ -529,7 +529,7 @@
         <v>198</v>
       </c>
       <c r="M2" t="n">
-        <v>10.0485</v>
+        <v>10.7148</v>
       </c>
       <c r="N2" t="n">
         <v>426</v>
@@ -538,219 +538,219 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.052</v>
+        <v>9.764900000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3508</v>
+        <v>2.5359</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2354</v>
+        <v>3.4464</v>
       </c>
       <c r="E3" t="n">
-        <v>9.052</v>
+        <v>9.764900000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2203</v>
+        <v>6.151</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8317</v>
+        <v>3.6139</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8823</v>
+        <v>7.3417</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9097</v>
+        <v>7.5286</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8317</v>
+        <v>3.6139</v>
       </c>
       <c r="K3" t="n">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="L3" t="n">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>9.741400000000001</v>
+        <v>11.1425</v>
       </c>
       <c r="N3" t="n">
-        <v>379</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.9276</v>
+        <v>9.089</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3185</v>
+        <v>2.3604</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1852</v>
+        <v>3.1771</v>
       </c>
       <c r="E4" t="n">
-        <v>8.9276</v>
+        <v>9.089</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3137</v>
+        <v>5.2572</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6139</v>
+        <v>3.8317</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0287</v>
+        <v>5.9402</v>
       </c>
       <c r="I4" t="n">
-        <v>6.1133</v>
+        <v>5.9902</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6139</v>
+        <v>3.8317</v>
       </c>
       <c r="K4" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="L4" t="n">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="M4" t="n">
-        <v>9.7272</v>
+        <v>9.821899999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>429</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.9631</v>
+        <v>7.9985</v>
       </c>
       <c r="C5" t="n">
-        <v>2.068</v>
+        <v>2.0772</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7956</v>
+        <v>2.7427</v>
       </c>
       <c r="E5" t="n">
-        <v>7.9631</v>
+        <v>7.9985</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8363</v>
+        <v>6.2704</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1268</v>
+        <v>1.7281</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8363</v>
+        <v>7.5289</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8628</v>
+        <v>7.7206</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1268</v>
+        <v>1.7281</v>
       </c>
       <c r="K5" t="n">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="L5" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="M5" t="n">
-        <v>7.9896</v>
+        <v>9.448700000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>426</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trk</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.3859</v>
+        <v>7.9615</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9181</v>
+        <v>2.0676</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5624</v>
+        <v>2.728</v>
       </c>
       <c r="E6" t="n">
-        <v>7.3859</v>
+        <v>7.9615</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7132</v>
+        <v>3.891</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6727</v>
+        <v>4.0705</v>
       </c>
       <c r="H6" t="n">
-        <v>5.0872</v>
+        <v>3.891</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1109</v>
+        <v>3.9568</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6727</v>
+        <v>4.0705</v>
       </c>
       <c r="K6" t="n">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="L6" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>7.7836</v>
+        <v>8.0273</v>
       </c>
       <c r="N6" t="n">
-        <v>399</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.3753</v>
+        <v>7.9423</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9154</v>
+        <v>2.0626</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5581</v>
+        <v>2.7203</v>
       </c>
       <c r="E7" t="n">
-        <v>7.3753</v>
+        <v>7.9423</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3048</v>
+        <v>2.8155</v>
       </c>
       <c r="G7" t="n">
-        <v>4.0705</v>
+        <v>5.1268</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3048</v>
+        <v>2.8155</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3357</v>
+        <v>2.8631</v>
       </c>
       <c r="J7" t="n">
-        <v>4.0705</v>
+        <v>5.1268</v>
       </c>
       <c r="K7" t="n">
         <v>228</v>
@@ -759,7 +759,7 @@
         <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>7.4062</v>
+        <v>7.9899</v>
       </c>
       <c r="N7" t="n">
         <v>426</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.9528</v>
+        <v>7.6616</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8056</v>
+        <v>1.9897</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3874</v>
+        <v>2.6085</v>
       </c>
       <c r="E8" t="n">
-        <v>6.9528</v>
+        <v>7.6616</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2247</v>
+        <v>2.5353</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7281</v>
+        <v>5.1263</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8893</v>
+        <v>2.5353</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9719</v>
+        <v>2.5782</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7281</v>
+        <v>5.1263</v>
       </c>
       <c r="K8" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="M8" t="n">
-        <v>7.699999999999999</v>
+        <v>7.704499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>268</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>trk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.8483</v>
+        <v>7.4925</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7785</v>
+        <v>1.9458</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3452</v>
+        <v>2.5411</v>
       </c>
       <c r="E9" t="n">
-        <v>6.8483</v>
+        <v>7.4925</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7221</v>
+        <v>4.8198</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1263</v>
+        <v>2.6727</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7221</v>
+        <v>5.2544</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7381</v>
+        <v>5.2986</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1263</v>
+        <v>2.6727</v>
       </c>
       <c r="K9" t="n">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="L9" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8644</v>
+        <v>7.9713</v>
       </c>
       <c r="N9" t="n">
-        <v>426</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8675</v>
+        <v>6.3783</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5238</v>
+        <v>1.6564</v>
       </c>
       <c r="D10" t="n">
-        <v>1.949</v>
+        <v>2.0972</v>
       </c>
       <c r="E10" t="n">
-        <v>5.8675</v>
+        <v>6.3783</v>
       </c>
       <c r="F10" t="n">
-        <v>5.3299</v>
+        <v>5.8407</v>
       </c>
       <c r="G10" t="n">
         <v>0.5376</v>
       </c>
       <c r="H10" t="n">
-        <v>6.0543</v>
+        <v>6.8552</v>
       </c>
       <c r="I10" t="n">
-        <v>6.1392</v>
+        <v>7.0297</v>
       </c>
       <c r="J10" t="n">
         <v>0.5376</v>
@@ -897,7 +897,7 @@
         <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>6.6768</v>
+        <v>7.5673</v>
       </c>
       <c r="N10" t="n">
         <v>268</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.5039</v>
+        <v>6.1422</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4294</v>
+        <v>1.5951</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8021</v>
+        <v>2.0031</v>
       </c>
       <c r="E11" t="n">
-        <v>5.5039</v>
+        <v>6.1422</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9701</v>
+        <v>3.0351</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5338</v>
+        <v>3.1071</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9701</v>
+        <v>3.0351</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0258</v>
+        <v>3.1124</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5338</v>
+        <v>3.1071</v>
       </c>
       <c r="K11" t="n">
         <v>231</v>
@@ -943,7 +943,7 @@
         <v>198</v>
       </c>
       <c r="M11" t="n">
-        <v>5.559600000000001</v>
+        <v>6.2195</v>
       </c>
       <c r="N11" t="n">
         <v>429</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.4942</v>
+        <v>5.5615</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4268</v>
+        <v>1.4443</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7982</v>
+        <v>1.7718</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4942</v>
+        <v>5.5615</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3871</v>
+        <v>4.0277</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1071</v>
+        <v>1.5338</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3871</v>
+        <v>4.0277</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4206</v>
+        <v>4.1302</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1071</v>
+        <v>1.5338</v>
       </c>
       <c r="K12" t="n">
         <v>231</v>
@@ -989,7 +989,7 @@
         <v>198</v>
       </c>
       <c r="M12" t="n">
-        <v>5.527699999999999</v>
+        <v>5.664000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>429</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.9852</v>
+        <v>5.3099</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2946</v>
+        <v>1.379</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5925</v>
+        <v>1.6716</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9852</v>
+        <v>5.3099</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7367</v>
+        <v>4.9414</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2485</v>
+        <v>0.3685</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1241</v>
+        <v>5.445</v>
       </c>
       <c r="I13" t="n">
-        <v>5.196</v>
+        <v>5.5837</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2485</v>
+        <v>0.3685</v>
       </c>
       <c r="K13" t="n">
         <v>194</v>
@@ -1035,7 +1035,7 @@
         <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4445</v>
+        <v>5.9522</v>
       </c>
       <c r="N13" t="n">
         <v>268</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.7655</v>
+        <v>5.1262</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2376</v>
+        <v>1.3313</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5038</v>
+        <v>1.5984</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7655</v>
+        <v>5.1262</v>
       </c>
       <c r="F14" t="n">
-        <v>4.397</v>
+        <v>4.8777</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3685</v>
+        <v>0.2485</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5915</v>
+        <v>5.3452</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6559</v>
+        <v>5.4813</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3685</v>
+        <v>0.2485</v>
       </c>
       <c r="K14" t="n">
         <v>194</v>
@@ -1081,7 +1081,7 @@
         <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>5.0244</v>
+        <v>5.7298</v>
       </c>
       <c r="N14" t="n">
         <v>268</v>
@@ -1090,967 +1090,967 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.6569</v>
+        <v>4.9277</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2094</v>
+        <v>1.2797</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4599</v>
+        <v>1.5193</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6569</v>
+        <v>4.9277</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0111</v>
+        <v>4.9277</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6458</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0111</v>
+        <v>5.4236</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0298</v>
+        <v>5.4236</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6458</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="L15" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6756</v>
+        <v>5.4236</v>
       </c>
       <c r="N15" t="n">
-        <v>379</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.333</v>
+        <v>4.6909</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1253</v>
+        <v>1.2182</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3291</v>
+        <v>1.4249</v>
       </c>
       <c r="E16" t="n">
-        <v>4.333</v>
+        <v>4.6909</v>
       </c>
       <c r="F16" t="n">
-        <v>4.333</v>
+        <v>4.0451</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
       <c r="H16" t="n">
-        <v>4.491</v>
+        <v>4.0451</v>
       </c>
       <c r="I16" t="n">
-        <v>4.491</v>
+        <v>4.0791</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.6458</v>
       </c>
       <c r="K16" t="n">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M16" t="n">
-        <v>4.491</v>
+        <v>4.724900000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>218</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.1725</v>
+        <v>4.6466</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0836</v>
+        <v>1.2067</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2642</v>
+        <v>1.4073</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1725</v>
+        <v>4.6466</v>
       </c>
       <c r="F17" t="n">
-        <v>4.4577</v>
+        <v>4.8667</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2852</v>
+        <v>-0.2201</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6866</v>
+        <v>5.3279</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7303</v>
+        <v>5.418</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2852</v>
+        <v>-0.2201</v>
       </c>
       <c r="K17" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4451</v>
+        <v>5.1979</v>
       </c>
       <c r="N17" t="n">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.0702</v>
+        <v>4.5499</v>
       </c>
       <c r="C18" t="n">
-        <v>1.057</v>
+        <v>1.1816</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2229</v>
+        <v>1.3688</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0702</v>
+        <v>4.5499</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2903</v>
+        <v>4.8351</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2201</v>
+        <v>-0.2852</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4242</v>
+        <v>5.2784</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4655</v>
+        <v>5.3677</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2201</v>
+        <v>-0.2852</v>
       </c>
       <c r="K18" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="L18" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>4.245399999999999</v>
+        <v>5.0825</v>
       </c>
       <c r="N18" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.0073</v>
+        <v>4.5406</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0407</v>
+        <v>1.1792</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1975</v>
+        <v>1.3651</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0073</v>
+        <v>4.5406</v>
       </c>
       <c r="F19" t="n">
-        <v>4.667</v>
+        <v>5.2963</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6597</v>
+        <v>-0.7557</v>
       </c>
       <c r="H19" t="n">
-        <v>5.0148</v>
+        <v>6.0016</v>
       </c>
       <c r="I19" t="n">
-        <v>5.0851</v>
+        <v>6.103</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6597</v>
+        <v>-0.7557</v>
       </c>
       <c r="K19" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="L19" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4254</v>
+        <v>5.3473</v>
       </c>
       <c r="N19" t="n">
-        <v>268</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.7324</v>
+        <v>4.1379</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.0746</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0864</v>
+        <v>1.2046</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7324</v>
+        <v>4.1379</v>
       </c>
       <c r="F20" t="n">
-        <v>4.4881</v>
+        <v>4.1379</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7557</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7344</v>
+        <v>4.1852</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7785</v>
+        <v>4.1852</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7557</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.0228</v>
+        <v>4.1852</v>
       </c>
       <c r="N20" t="n">
-        <v>287</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.345</v>
+        <v>4.1064</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8687</v>
+        <v>1.0664</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9298999999999999</v>
+        <v>1.1921</v>
       </c>
       <c r="E21" t="n">
-        <v>3.345</v>
+        <v>4.1064</v>
       </c>
       <c r="F21" t="n">
-        <v>1.901</v>
+        <v>4.7661</v>
       </c>
       <c r="G21" t="n">
-        <v>1.444</v>
+        <v>-0.6597</v>
       </c>
       <c r="H21" t="n">
-        <v>1.901</v>
+        <v>5.1701</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9276</v>
+        <v>5.3018</v>
       </c>
       <c r="J21" t="n">
-        <v>1.444</v>
+        <v>-0.6597</v>
       </c>
       <c r="K21" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="L21" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3716</v>
+        <v>4.6421</v>
       </c>
       <c r="N21" t="n">
-        <v>429</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8278</v>
+        <v>0.9538</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8663</v>
+        <v>1.0194</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="I22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1874</v>
+        <v>3.6729</v>
       </c>
       <c r="N22" t="n">
-        <v>177</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9348</v>
+        <v>3.3719</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7622</v>
+        <v>0.8757</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7642</v>
+        <v>0.8995</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9348</v>
+        <v>3.3719</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0589</v>
+        <v>3.1521</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8759</v>
+        <v>0.2198</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0589</v>
+        <v>3.1521</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0684</v>
+        <v>3.2054</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8759</v>
+        <v>0.2198</v>
       </c>
       <c r="K23" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="L23" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9443</v>
+        <v>3.4252</v>
       </c>
       <c r="N23" t="n">
-        <v>379</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>iDk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8363</v>
+        <v>3.3528</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7366</v>
+        <v>0.8707</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7244</v>
+        <v>0.8918</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8363</v>
+        <v>3.3528</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8363</v>
+        <v>3.9668</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8363</v>
+        <v>3.9668</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8363</v>
+        <v>4.0002</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="K24" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8363</v>
+        <v>3.386200000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>230</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hatz</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6169</v>
+        <v>3.337</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6796</v>
+        <v>0.8666</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6358</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6169</v>
+        <v>3.337</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6169</v>
+        <v>1.893</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6169</v>
+        <v>1.893</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6169</v>
+        <v>1.9412</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="K25" t="n">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6169</v>
+        <v>3.3852</v>
       </c>
       <c r="N25" t="n">
-        <v>177</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>to1nou</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.5462</v>
+        <v>3.3048</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6612</v>
+        <v>0.8583</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6072</v>
+        <v>0.8727</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5462</v>
+        <v>3.3048</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5462</v>
+        <v>3.3938</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5462</v>
+        <v>3.3938</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5462</v>
+        <v>3.4511</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="K26" t="n">
         <v>218</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>2.5462</v>
+        <v>3.3621</v>
       </c>
       <c r="N26" t="n">
-        <v>218</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.5068</v>
+        <v>3.1874</v>
       </c>
       <c r="C27" t="n">
-        <v>0.651</v>
+        <v>0.8278</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5913</v>
+        <v>0.826</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5068</v>
+        <v>3.1874</v>
       </c>
       <c r="F27" t="n">
-        <v>2.287</v>
+        <v>3.1874</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2198</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.287</v>
+        <v>3.1874</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3083</v>
+        <v>3.1874</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2198</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5281</v>
+        <v>3.1874</v>
       </c>
       <c r="N27" t="n">
-        <v>274</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iDk</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4884</v>
+        <v>2.9614</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6462</v>
+        <v>0.7691</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5839</v>
+        <v>0.7359</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4884</v>
+        <v>2.9614</v>
       </c>
       <c r="F28" t="n">
-        <v>3.1024</v>
+        <v>2.9614</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1024</v>
+        <v>2.9614</v>
       </c>
       <c r="I28" t="n">
-        <v>3.1168</v>
+        <v>2.9614</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="L28" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5028</v>
+        <v>2.9614</v>
       </c>
       <c r="N28" t="n">
-        <v>399</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4513</v>
+        <v>2.9271</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.7602</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5689</v>
+        <v>0.7222</v>
       </c>
       <c r="E29" t="n">
-        <v>2.4513</v>
+        <v>2.9271</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5403</v>
+        <v>2.0512</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.089</v>
+        <v>0.8759</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5403</v>
+        <v>2.0512</v>
       </c>
       <c r="I29" t="n">
-        <v>2.564</v>
+        <v>2.0684</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.089</v>
+        <v>0.8759</v>
       </c>
       <c r="K29" t="n">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M29" t="n">
-        <v>2.475</v>
+        <v>2.9443</v>
       </c>
       <c r="N29" t="n">
-        <v>274</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>to1nou</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3418</v>
+        <v>2.8311</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6082</v>
+        <v>0.7352</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3418</v>
+        <v>2.8311</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8315</v>
+        <v>2.8311</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4897</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.8315</v>
+        <v>2.8311</v>
       </c>
       <c r="I30" t="n">
-        <v>2.8315</v>
+        <v>2.8311</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4897</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="L30" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3418</v>
+        <v>2.8311</v>
       </c>
       <c r="N30" t="n">
-        <v>326</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3241</v>
+        <v>2.7435</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6036</v>
+        <v>0.7125</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5175</v>
+        <v>0.6491</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3241</v>
+        <v>2.7435</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3241</v>
+        <v>3.2332</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.4897</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3241</v>
+        <v>3.2332</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3241</v>
+        <v>3.2332</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.4897</v>
       </c>
       <c r="K31" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M31" t="n">
-        <v>2.3241</v>
+        <v>2.7435</v>
       </c>
       <c r="N31" t="n">
-        <v>218</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>Hatz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5686</v>
+        <v>0.6796</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4631</v>
+        <v>0.5987</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="I32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.1893</v>
+        <v>2.6169</v>
       </c>
       <c r="N32" t="n">
-        <v>226</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.0417</v>
+        <v>2.2644</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5302</v>
+        <v>0.5881</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4034</v>
+        <v>0.4582</v>
       </c>
       <c r="E33" t="n">
-        <v>2.0417</v>
+        <v>2.2644</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0417</v>
+        <v>2.1766</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0878</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0417</v>
+        <v>2.1766</v>
       </c>
       <c r="I33" t="n">
-        <v>2.0417</v>
+        <v>2.2134</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.0878</v>
       </c>
       <c r="K33" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>2.0417</v>
+        <v>2.3012</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.8378</v>
+        <v>2.1339</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4773</v>
+        <v>0.5542</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3211</v>
+        <v>0.4062</v>
       </c>
       <c r="E34" t="n">
-        <v>1.8378</v>
+        <v>2.1339</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8378</v>
+        <v>2.5827</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.4488</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8378</v>
+        <v>2.5827</v>
       </c>
       <c r="I34" t="n">
-        <v>1.8378</v>
+        <v>2.5827</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.4488</v>
       </c>
       <c r="K34" t="n">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M34" t="n">
-        <v>1.8378</v>
+        <v>2.1339</v>
       </c>
       <c r="N34" t="n">
-        <v>227</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>glow</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.8228</v>
+        <v>2.0417</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4734</v>
+        <v>0.5302</v>
       </c>
       <c r="D35" t="n">
-        <v>0.315</v>
+        <v>0.3695</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8228</v>
+        <v>2.0417</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8742</v>
+        <v>2.0417</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0514</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8742</v>
+        <v>2.0417</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8917</v>
+        <v>2.0417</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0514</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>227</v>
+        <v>165</v>
       </c>
       <c r="L35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.8403</v>
+        <v>2.0417</v>
       </c>
       <c r="N35" t="n">
-        <v>287</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.7754</v>
+        <v>1.9572</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4611</v>
+        <v>0.5083</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2959</v>
+        <v>0.3358</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7754</v>
+        <v>1.9572</v>
       </c>
       <c r="F36" t="n">
-        <v>2.2462</v>
+        <v>2.428</v>
       </c>
       <c r="G36" t="n">
         <v>-0.4708</v>
       </c>
       <c r="H36" t="n">
-        <v>2.2462</v>
+        <v>2.428</v>
       </c>
       <c r="I36" t="n">
-        <v>2.2777</v>
+        <v>2.4898</v>
       </c>
       <c r="J36" t="n">
         <v>-0.4708</v>
@@ -2093,7 +2093,7 @@
         <v>198</v>
       </c>
       <c r="M36" t="n">
-        <v>1.8069</v>
+        <v>2.019</v>
       </c>
       <c r="N36" t="n">
         <v>429</v>
@@ -2102,584 +2102,584 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.6278</v>
+        <v>1.8666</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4227</v>
+        <v>0.4848</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2362</v>
+        <v>0.2997</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6278</v>
+        <v>1.8666</v>
       </c>
       <c r="F37" t="n">
-        <v>1.54</v>
+        <v>1.8666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0878</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.54</v>
+        <v>1.8666</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5544</v>
+        <v>1.8666</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0878</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="L37" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.6422</v>
+        <v>1.8666</v>
       </c>
       <c r="N37" t="n">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maluk3</t>
+          <t>EasTor</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.5884</v>
+        <v>1.8459</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4125</v>
+        <v>0.4794</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2203</v>
+        <v>0.2915</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5884</v>
+        <v>1.8459</v>
       </c>
       <c r="F38" t="n">
-        <v>2.3754</v>
+        <v>1.8459</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.787</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.3754</v>
+        <v>1.8459</v>
       </c>
       <c r="I38" t="n">
-        <v>2.3864</v>
+        <v>1.8459</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.787</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="L38" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.5994</v>
+        <v>1.8459</v>
       </c>
       <c r="N38" t="n">
-        <v>399</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>glow</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.4356</v>
+        <v>1.8432</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3728</v>
+        <v>0.4787</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1586</v>
+        <v>0.2904</v>
       </c>
       <c r="E39" t="n">
-        <v>1.4356</v>
+        <v>1.8432</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4356</v>
+        <v>1.8946</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.0514</v>
       </c>
       <c r="H39" t="n">
-        <v>2.4356</v>
+        <v>1.8946</v>
       </c>
       <c r="I39" t="n">
-        <v>2.4583</v>
+        <v>1.9266</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.0514</v>
       </c>
       <c r="K39" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="L39" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4583</v>
+        <v>1.8752</v>
       </c>
       <c r="N39" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Polox</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3652</v>
+        <v>0.4543</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1468</v>
+        <v>0.253</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="I40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4064</v>
+        <v>1.7493</v>
       </c>
       <c r="N40" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EasTor</t>
+          <t>Polox</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="C41" t="n">
-        <v>0.348</v>
+        <v>0.4347</v>
       </c>
       <c r="D41" t="n">
-        <v>0.12</v>
+        <v>0.223</v>
       </c>
       <c r="E41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="I41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.3402</v>
+        <v>1.6739</v>
       </c>
       <c r="N41" t="n">
-        <v>230</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOKER</t>
+          <t>effys</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3435</v>
+        <v>0.4185</v>
       </c>
       <c r="D42" t="n">
-        <v>0.113</v>
+        <v>0.198</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3228</v>
+        <v>1.6113</v>
       </c>
       <c r="N42" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BURNRUOk</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="C43" t="n">
-        <v>0.29</v>
+        <v>0.412</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0297</v>
+        <v>0.1882</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="F43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1165</v>
+        <v>1.5866</v>
       </c>
       <c r="N43" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>Maluk3</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1037</v>
+        <v>1.5795</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2866</v>
+        <v>0.4102</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0245</v>
+        <v>0.1854</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1037</v>
+        <v>1.5795</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5525</v>
+        <v>2.3665</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.4488</v>
+        <v>-0.787</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5525</v>
+        <v>2.3665</v>
       </c>
       <c r="I44" t="n">
-        <v>1.5525</v>
+        <v>2.3864</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.4488</v>
+        <v>-0.787</v>
       </c>
       <c r="K44" t="n">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="L44" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1037</v>
+        <v>1.5994</v>
       </c>
       <c r="N44" t="n">
-        <v>326</v>
+        <v>399</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.0202</v>
+        <v>1.4657</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2649</v>
+        <v>0.3806</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0092</v>
+        <v>0.14</v>
       </c>
       <c r="E45" t="n">
-        <v>1.0202</v>
+        <v>1.4657</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0202</v>
+        <v>2.4657</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0202</v>
+        <v>2.4657</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0202</v>
+        <v>2.5073</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M45" t="n">
-        <v>1.0202</v>
+        <v>1.5073</v>
       </c>
       <c r="N45" t="n">
-        <v>226</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>BURNRUOk</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9588</v>
+        <v>1.4559</v>
       </c>
       <c r="C46" t="n">
-        <v>0.249</v>
+        <v>0.3781</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.034</v>
+        <v>0.1361</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9588</v>
+        <v>1.4559</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0913</v>
+        <v>1.4559</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1325</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0913</v>
+        <v>1.4559</v>
       </c>
       <c r="I46" t="n">
-        <v>1.0964</v>
+        <v>1.4559</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.1325</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="L46" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9639</v>
+        <v>1.4559</v>
       </c>
       <c r="N46" t="n">
-        <v>379</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>effys</t>
+          <t>LoWkii</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2443</v>
+        <v>0.3595</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0414</v>
+        <v>0.1076</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9406</v>
+        <v>1.3842</v>
       </c>
       <c r="N47" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>SOKER</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2423</v>
+        <v>0.3438</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0445</v>
+        <v>0.0835</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9329</v>
+        <v>1.3237</v>
       </c>
       <c r="N48" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2251</v>
+        <v>0.3125</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0712</v>
+        <v>0.0355</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8668</v>
+        <v>1.2033</v>
       </c>
       <c r="N49" t="n">
         <v>165</v>
@@ -2700,1749 +2700,1749 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>bnwGiggs</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2152</v>
+        <v>0.2652</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0867</v>
+        <v>-0.037</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="I50" t="n">
-        <v>1.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="L50" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8285</v>
+        <v>1.0213</v>
       </c>
       <c r="N50" t="n">
-        <v>326</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1894</v>
+        <v>0.2591</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1267</v>
+        <v>-0.0464</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.9977</v>
       </c>
       <c r="N51" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LoWkii</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6963</v>
+        <v>0.9548</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1808</v>
+        <v>0.248</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1401</v>
+        <v>-0.0635</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6963</v>
+        <v>0.9548</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6963</v>
+        <v>1.0873</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.1325</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6963</v>
+        <v>1.0873</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6963</v>
+        <v>1.0964</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.1325</v>
       </c>
       <c r="K52" t="n">
-        <v>93</v>
+        <v>248</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6963</v>
+        <v>0.9639</v>
       </c>
       <c r="N52" t="n">
-        <v>93</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6065</v>
+        <v>0.8618</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1575</v>
+        <v>0.2238</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1763</v>
+        <v>-0.1006</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6065</v>
+        <v>0.8618</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6065</v>
+        <v>1.8618</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6065</v>
+        <v>1.8618</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6065</v>
+        <v>1.8618</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K53" t="n">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6065</v>
+        <v>0.8617999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>53</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TenZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1559</v>
+        <v>0.1894</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1788</v>
+        <v>-0.1534</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6005</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bnwGiggs</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1239</v>
+        <v>0.1629</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2286</v>
+        <v>-0.194</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4772</v>
+        <v>0.6273</v>
       </c>
       <c r="N55" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>TenZ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1046</v>
+        <v>0.1615</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2587</v>
+        <v>-0.1962</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4026</v>
+        <v>0.6218</v>
       </c>
       <c r="N56" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>solo</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3425</v>
+        <v>0.6065</v>
       </c>
       <c r="C57" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1575</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.283</v>
+        <v>-0.2023</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3425</v>
+        <v>0.6065</v>
       </c>
       <c r="F57" t="n">
-        <v>1.2221</v>
+        <v>0.6065</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.8796</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1.2221</v>
+        <v>0.6065</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2335</v>
+        <v>0.6065</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.8796</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>227</v>
+        <v>53</v>
       </c>
       <c r="L57" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3539</v>
+        <v>0.6065</v>
       </c>
       <c r="N57" t="n">
-        <v>287</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>caike</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3109</v>
+        <v>0.5825</v>
       </c>
       <c r="C58" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1513</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.2958</v>
+        <v>-0.2118</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3109</v>
+        <v>0.5825</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3109</v>
+        <v>2.5729</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-1.9904</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3109</v>
+        <v>2.5729</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3109</v>
+        <v>2.5946</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-1.9904</v>
       </c>
       <c r="K58" t="n">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3109</v>
+        <v>0.6041999999999998</v>
       </c>
       <c r="N58" t="n">
-        <v>165</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0798</v>
+        <v>0.134</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.2972</v>
+        <v>-0.2384</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>226</v>
+        <v>165</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3074</v>
+        <v>0.5158</v>
       </c>
       <c r="N59" t="n">
-        <v>226</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TOAO</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2683</v>
+        <v>0.403</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0697</v>
+        <v>0.1047</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.313</v>
+        <v>-0.2834</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2683</v>
+        <v>0.403</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3184</v>
+        <v>0.403</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.0501</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3184</v>
+        <v>0.403</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3184</v>
+        <v>0.403</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.0501</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2683</v>
+        <v>0.403</v>
       </c>
       <c r="N60" t="n">
-        <v>326</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>TOAO</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2635</v>
+        <v>0.3428</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0684</v>
+        <v>0.089</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3149</v>
+        <v>-0.3073</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2635</v>
+        <v>0.3428</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2635</v>
+        <v>0.3929</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.0501</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2635</v>
+        <v>0.3929</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2635</v>
+        <v>0.3929</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.0501</v>
       </c>
       <c r="K61" t="n">
-        <v>65</v>
+        <v>244</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2635</v>
+        <v>0.3428</v>
       </c>
       <c r="N61" t="n">
-        <v>65</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NikoM</t>
+          <t>solo</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.245</v>
+        <v>0.3334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0636</v>
+        <v>0.0866</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3224</v>
+        <v>-0.3111</v>
       </c>
       <c r="E62" t="n">
-        <v>0.245</v>
+        <v>0.3334</v>
       </c>
       <c r="F62" t="n">
-        <v>0.245</v>
+        <v>1.213</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.8796</v>
       </c>
       <c r="H62" t="n">
-        <v>0.245</v>
+        <v>1.213</v>
       </c>
       <c r="I62" t="n">
-        <v>0.245</v>
+        <v>1.2335</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.8796</v>
       </c>
       <c r="K62" t="n">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M62" t="n">
-        <v>0.245</v>
+        <v>0.3539</v>
       </c>
       <c r="N62" t="n">
-        <v>76</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ryann</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0576</v>
+        <v>0.0798</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3318</v>
+        <v>-0.3214</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.2218</v>
+        <v>0.3074</v>
       </c>
       <c r="N63" t="n">
-        <v>81</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Laz</t>
+          <t>NikoM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0525</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.3396</v>
+        <v>-0.3461</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.2023</v>
+        <v>0.2454</v>
       </c>
       <c r="N64" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>moxie</t>
+          <t>ryann</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0076</v>
+        <v>0.0576</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.4095</v>
+        <v>-0.3555</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0293</v>
+        <v>0.2218</v>
       </c>
       <c r="N65" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Laz</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0009</v>
+        <v>0.0525</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.4227</v>
+        <v>-0.3633</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.0033</v>
+        <v>0.2023</v>
       </c>
       <c r="N66" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>ImpressioN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0034</v>
+        <v>0.0426</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.4266</v>
+        <v>-0.3785</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.0129</v>
+        <v>0.1642</v>
       </c>
       <c r="N67" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vek</t>
+          <t>moxie</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.4336</v>
+        <v>-0.4322</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.0303</v>
+        <v>0.0293</v>
       </c>
       <c r="N68" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>s550</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.016</v>
+        <v>-0.0034</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.4462</v>
+        <v>-0.449</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.0615</v>
+        <v>-0.0129</v>
       </c>
       <c r="N69" t="n">
-        <v>160</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kntz</t>
+          <t>vek</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0186</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.4503</v>
+        <v>-0.456</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.0716</v>
+        <v>-0.0303</v>
       </c>
       <c r="N70" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>s550</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.026</v>
+        <v>-0.016</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.4619</v>
+        <v>-0.4684</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.1003</v>
+        <v>-0.0615</v>
       </c>
       <c r="N71" t="n">
-        <v>53</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Kntz</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.0318</v>
+        <v>-0.0186</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4708</v>
+        <v>-0.4724</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.1225</v>
+        <v>-0.0716</v>
       </c>
       <c r="N72" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ImpressioN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0401</v>
+        <v>-0.026</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.4838</v>
+        <v>-0.4839</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.1545</v>
+        <v>-0.1003</v>
       </c>
       <c r="N73" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>caike</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.1828</v>
+        <v>-0.1225</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0475</v>
+        <v>-0.0318</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.4952</v>
+        <v>-0.4927</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1828</v>
+        <v>-0.1225</v>
       </c>
       <c r="F74" t="n">
-        <v>1.8076</v>
+        <v>-0.1225</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.9904</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1.8076</v>
+        <v>-0.1225</v>
       </c>
       <c r="I74" t="n">
-        <v>1.816</v>
+        <v>-0.1225</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.9904</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>280</v>
+        <v>164</v>
       </c>
       <c r="L74" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.1743999999999999</v>
+        <v>-0.1225</v>
       </c>
       <c r="N74" t="n">
-        <v>399</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SileNt</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0494</v>
+        <v>-0.0388</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.4982</v>
+        <v>-0.5034</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.1901</v>
+        <v>-0.1494</v>
       </c>
       <c r="N75" t="n">
-        <v>81</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>SileNt</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.0519</v>
+        <v>-0.0494</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.5021</v>
+        <v>-0.5196</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.1999</v>
+        <v>-0.1901</v>
       </c>
       <c r="N76" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.0531</v>
+        <v>-0.05</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.5039</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.2044</v>
+        <v>-0.1927</v>
       </c>
       <c r="N77" t="n">
-        <v>78</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.0575</v>
+        <v>-0.0519</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.5108</v>
+        <v>-0.5236</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.2215</v>
+        <v>-0.1999</v>
       </c>
       <c r="N78" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0531</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.5303</v>
+        <v>-0.5253</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.2697</v>
+        <v>-0.2044</v>
       </c>
       <c r="N79" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.0703</v>
+        <v>-0.0575</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5322</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.2706</v>
+        <v>-0.2215</v>
       </c>
       <c r="N80" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dmm</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.5363</v>
+        <v>-0.5506</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.2844</v>
+        <v>-0.2678</v>
       </c>
       <c r="N81" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kairi</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0779</v>
+        <v>-0.0703</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.5426</v>
+        <v>-0.5517</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.3</v>
+        <v>-0.2706</v>
       </c>
       <c r="N82" t="n">
-        <v>230</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>dmm</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.0896</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.5608</v>
+        <v>-0.5572</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.3451</v>
+        <v>-0.2844</v>
       </c>
       <c r="N83" t="n">
-        <v>226</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nbl</t>
+          <t>Kairi</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.097</v>
+        <v>-0.0779</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.5723</v>
+        <v>-0.5634</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.3736</v>
+        <v>-0.3</v>
       </c>
       <c r="N84" t="n">
-        <v>76</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.0993</v>
+        <v>-0.0896</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.5758</v>
+        <v>-0.5814</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.3822</v>
+        <v>-0.3451</v>
       </c>
       <c r="N85" t="n">
-        <v>78</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>nbl</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.1039</v>
+        <v>-0.097</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.583</v>
+        <v>-0.5928</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.4002</v>
+        <v>-0.3736</v>
       </c>
       <c r="N86" t="n">
-        <v>177</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.1072</v>
+        <v>-0.0993</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.5881</v>
+        <v>-0.5962</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.4127</v>
+        <v>-0.3822</v>
       </c>
       <c r="N87" t="n">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88">
@@ -4458,7 +4458,7 @@
         <v>-0.1097</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="E88" t="n">
         <v>-0.4224</v>
@@ -4504,7 +4504,7 @@
         <v>-0.1203</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6284</v>
       </c>
       <c r="E89" t="n">
         <v>-0.4631</v>
@@ -4550,7 +4550,7 @@
         <v>-0.1243</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.6147</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E90" t="n">
         <v>-0.4787</v>
@@ -4586,952 +4586,952 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Zellsis</t>
+          <t>cardiac</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.1297</v>
+        <v>-0.1257</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.6232</v>
+        <v>-0.6367</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.4996</v>
+        <v>-0.484</v>
       </c>
       <c r="N91" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RaZ</t>
+          <t>Zellsis</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.1331</v>
+        <v>-0.1297</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.643</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.5127</v>
+        <v>-0.4996</v>
       </c>
       <c r="N92" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MAIROLLS</t>
+          <t>RaZ</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1369</v>
+        <v>-0.1331</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.6343</v>
+        <v>-0.6482</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.5271</v>
+        <v>-0.5127</v>
       </c>
       <c r="N93" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Zote</t>
+          <t>MAIROLLS</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.1417</v>
+        <v>-0.1369</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.6417</v>
+        <v>-0.6539</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.5455</v>
+        <v>-0.5271</v>
       </c>
       <c r="N94" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>n1ck</t>
+          <t>Zote</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.1529</v>
+        <v>-0.1417</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.6593</v>
+        <v>-0.6612</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.5889</v>
+        <v>-0.5455</v>
       </c>
       <c r="N95" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cardiac</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.6152</v>
+        <v>-0.5793</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.1598</v>
+        <v>-0.1504</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6747</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.6152</v>
+        <v>-0.5793</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.6152</v>
+        <v>0.8142</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>-1.3935</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.6152</v>
+        <v>0.8142</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6152</v>
+        <v>0.828</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>-1.3935</v>
       </c>
       <c r="K96" t="n">
-        <v>65</v>
+        <v>228</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.6152</v>
+        <v>-0.5655</v>
       </c>
       <c r="N96" t="n">
-        <v>65</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LILMAN</t>
+          <t>n1ck</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.1674</v>
+        <v>-0.1529</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.6818</v>
+        <v>-0.6785</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.6446</v>
+        <v>-0.5889</v>
       </c>
       <c r="N97" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kan4</t>
+          <t>mch</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.7299</v>
+        <v>-0.6148</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.1896</v>
+        <v>-0.1597</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6888</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.7299</v>
+        <v>-0.6148</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.7299</v>
+        <v>0.9065</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>-1.5213</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.7299</v>
+        <v>0.9065</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.7299</v>
+        <v>0.9141</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>-1.5213</v>
       </c>
       <c r="K98" t="n">
-        <v>93</v>
+        <v>280</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.7299</v>
+        <v>-0.6072000000000001</v>
       </c>
       <c r="N98" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>LILMAN</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.7512</v>
+        <v>-0.6446</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.1951</v>
+        <v>-0.1674</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.7248</v>
+        <v>-0.7007</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.7512</v>
+        <v>-0.6446</v>
       </c>
       <c r="F99" t="n">
-        <v>0.6423</v>
+        <v>-0.6446</v>
       </c>
       <c r="G99" t="n">
-        <v>-1.3935</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.6423</v>
+        <v>-0.6446</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6483</v>
+        <v>-0.6446</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.3935</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>228</v>
+        <v>72</v>
       </c>
       <c r="L99" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.7452</v>
+        <v>-0.6446</v>
       </c>
       <c r="N99" t="n">
-        <v>426</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>els</t>
+          <t>roseau</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.2108</v>
+        <v>-0.1732</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.7494</v>
+        <v>-0.7096</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.8119</v>
+        <v>-0.667</v>
       </c>
       <c r="N100" t="n">
-        <v>72</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sys</t>
+          <t>Kan4</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.2177</v>
+        <v>-0.1896</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.76</v>
+        <v>-0.7347</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.8383</v>
+        <v>-0.7299</v>
       </c>
       <c r="N101" t="n">
-        <v>227</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>els</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.2198</v>
+        <v>-0.2108</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.7632</v>
+        <v>-0.7674</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8119</v>
       </c>
       <c r="N102" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>luckeRRR</t>
+          <t>Sys</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.2207</v>
+        <v>-0.2177</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7779</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>-0.8497</v>
+        <v>-0.8383</v>
       </c>
       <c r="N103" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Gn</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.227</v>
+        <v>-0.2198</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.7744</v>
+        <v>-0.7811</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.8739</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="N104" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>emagine</t>
+          <t>luckeRRR</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.2348</v>
+        <v>-0.2207</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.7866</v>
+        <v>-0.7824</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>-0.9041</v>
+        <v>-0.8497</v>
       </c>
       <c r="N105" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Noktse</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.2442</v>
+        <v>-0.227</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.8012</v>
+        <v>-0.7921</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.9402</v>
+        <v>-0.8739</v>
       </c>
       <c r="N106" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>takej</t>
+          <t>Eeyore</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.2449</v>
+        <v>-0.23</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.8023</v>
+        <v>-0.7967</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.9429</v>
+        <v>-0.8855</v>
       </c>
       <c r="N107" t="n">
-        <v>72</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OCEAN</t>
+          <t>emagine</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.2449</v>
+        <v>-0.2348</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.8024</v>
+        <v>-0.8041</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.9431</v>
+        <v>-0.9041</v>
       </c>
       <c r="N108" t="n">
-        <v>72</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>Noktse</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2614</v>
+        <v>-0.2442</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.8279</v>
+        <v>-0.8185</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="F109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-1.0064</v>
+        <v>-0.9402</v>
       </c>
       <c r="N109" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Benkai</t>
+          <t>takej</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.2626</v>
+        <v>-0.2449</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.8299</v>
+        <v>-0.8196</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="I110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-1.0113</v>
+        <v>-0.9429</v>
       </c>
       <c r="N110" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>crow</t>
+          <t>OCEAN</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2739</v>
+        <v>-0.2449</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.8474</v>
+        <v>-0.8196</v>
       </c>
       <c r="E111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-1.0546</v>
+        <v>-0.9431</v>
       </c>
       <c r="N111" t="n">
         <v>72</v>
@@ -5552,78 +5552,78 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.2742</v>
+        <v>-0.2614</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.8479</v>
+        <v>-0.8449</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="F112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.0558</v>
+        <v>-1.0064</v>
       </c>
       <c r="N112" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>splashske</t>
+          <t>Benkai</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.2859</v>
+        <v>-0.2626</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.8661</v>
+        <v>-0.8468</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="I113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-1.1009</v>
+        <v>-1.0113</v>
       </c>
       <c r="N113" t="n">
         <v>73</v>
@@ -5644,599 +5644,599 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>tb</t>
+          <t>crow</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.2865</v>
+        <v>-0.2739</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.867</v>
+        <v>-0.8641</v>
       </c>
       <c r="E114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="I114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>-1.1031</v>
+        <v>-1.0546</v>
       </c>
       <c r="N114" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-1.1229</v>
+        <v>-1.0558</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.2916</v>
+        <v>-0.2742</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.875</v>
+        <v>-0.8645</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.1229</v>
+        <v>-1.0558</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.7904</v>
+        <v>-1.0558</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6675</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-1.7904</v>
+        <v>-1.0558</v>
       </c>
       <c r="I115" t="n">
-        <v>-1.7904</v>
+        <v>-1.0558</v>
       </c>
       <c r="J115" t="n">
-        <v>0.6675</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>244</v>
+        <v>73</v>
       </c>
       <c r="L115" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-1.1229</v>
+        <v>-1.0558</v>
       </c>
       <c r="N115" t="n">
-        <v>326</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>hooch</t>
+          <t>splashske</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-1.1946</v>
+        <v>-1.1009</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.3102</v>
+        <v>-0.2859</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.904</v>
+        <v>-0.8825</v>
       </c>
       <c r="E116" t="n">
-        <v>-1.1946</v>
+        <v>-1.1009</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8054</v>
+        <v>-1.1009</v>
       </c>
       <c r="G116" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.8054</v>
+        <v>-1.1009</v>
       </c>
       <c r="I116" t="n">
-        <v>0.8091</v>
+        <v>-1.1009</v>
       </c>
       <c r="J116" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>248</v>
+        <v>73</v>
       </c>
       <c r="L116" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-1.1909</v>
+        <v>-1.1009</v>
       </c>
       <c r="N116" t="n">
-        <v>379</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ViperDemon</t>
+          <t>tb</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.3195</v>
+        <v>-0.2865</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.9183</v>
+        <v>-0.8834</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="F117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="I117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-1.2302</v>
+        <v>-1.1031</v>
       </c>
       <c r="N117" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>mch</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-1.2433</v>
+        <v>-1.1229</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.3229</v>
+        <v>-0.2916</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.9236</v>
+        <v>-0.8913</v>
       </c>
       <c r="E118" t="n">
-        <v>-1.2433</v>
+        <v>-1.1229</v>
       </c>
       <c r="F118" t="n">
-        <v>0.278</v>
+        <v>-1.7904</v>
       </c>
       <c r="G118" t="n">
-        <v>-1.5213</v>
+        <v>0.6675</v>
       </c>
       <c r="H118" t="n">
-        <v>0.278</v>
+        <v>-1.7904</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2793</v>
+        <v>-1.7904</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.5213</v>
+        <v>0.6675</v>
       </c>
       <c r="K118" t="n">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="L118" t="n">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="M118" t="n">
-        <v>-1.242</v>
+        <v>-1.1229</v>
       </c>
       <c r="N118" t="n">
-        <v>399</v>
+        <v>326</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>hooch</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-1.3225</v>
+        <v>-1.1977</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.3435</v>
+        <v>-0.311</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.9556</v>
+        <v>-0.9211</v>
       </c>
       <c r="E119" t="n">
-        <v>-1.3225</v>
+        <v>-1.1977</v>
       </c>
       <c r="F119" t="n">
-        <v>-1.3225</v>
+        <v>0.8023</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.3225</v>
+        <v>0.8023</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.3225</v>
+        <v>0.8091</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K119" t="n">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M119" t="n">
-        <v>-1.3225</v>
+        <v>-1.1909</v>
       </c>
       <c r="N119" t="n">
-        <v>81</v>
+        <v>379</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>ViperDemon</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3483</v>
+        <v>-0.3195</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.9631</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="F120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="I120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>-1.3411</v>
+        <v>-1.2302</v>
       </c>
       <c r="N120" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Max0b</t>
+          <t>YOUYOU</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.3536</v>
+        <v>-0.3207</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.9714</v>
+        <v>-0.9359</v>
       </c>
       <c r="E121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="F121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>93</v>
+        <v>218</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>-1.3615</v>
+        <v>-1.235</v>
       </c>
       <c r="N121" t="n">
-        <v>93</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>barce</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.3597</v>
+        <v>-0.3435</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="E122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="F122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="I122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>-1.3849</v>
+        <v>-1.3225</v>
       </c>
       <c r="N122" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>roseau</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.3712</v>
+        <v>-0.3483</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.9988</v>
+        <v>-0.9782</v>
       </c>
       <c r="E123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="F123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="I123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>227</v>
+        <v>65</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>-1.4294</v>
+        <v>-1.3411</v>
       </c>
       <c r="N123" t="n">
-        <v>227</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>YOUYOU</t>
+          <t>Max0b</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.3946</v>
+        <v>-0.3536</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.0351</v>
+        <v>-0.9863</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>-1.5193</v>
+        <v>-1.3615</v>
       </c>
       <c r="N124" t="n">
-        <v>218</v>
+        <v>93</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>barce</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.4308</v>
+        <v>-0.3597</v>
       </c>
       <c r="D125" t="n">
-        <v>-1.0914</v>
+        <v>-0.9957</v>
       </c>
       <c r="E125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="F125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="I125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>-1.6587</v>
+        <v>-1.3849</v>
       </c>
       <c r="N125" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Eeyore</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.4508</v>
+        <v>-0.4308</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.1226</v>
+        <v>-1.1047</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="F126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>227</v>
+        <v>53</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>-1.7358</v>
+        <v>-1.6587</v>
       </c>
       <c r="N126" t="n">
-        <v>227</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127">
@@ -6252,7 +6252,7 @@
         <v>-0.453</v>
       </c>
       <c r="D127" t="n">
-        <v>-1.1261</v>
+        <v>-1.1389</v>
       </c>
       <c r="E127" t="n">
         <v>-1.7445</v>
@@ -6298,7 +6298,7 @@
         <v>-0.4697</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.1521</v>
+        <v>-1.1645</v>
       </c>
       <c r="E128" t="n">
         <v>-1.8088</v>
@@ -6344,7 +6344,7 @@
         <v>-0.5066000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.2094</v>
+        <v>-1.2211</v>
       </c>
       <c r="E129" t="n">
         <v>-1.9508</v>
@@ -6390,7 +6390,7 @@
         <v>-0.5189</v>
       </c>
       <c r="D130" t="n">
-        <v>-1.2286</v>
+        <v>-1.24</v>
       </c>
       <c r="E130" t="n">
         <v>-1.9982</v>
@@ -6436,7 +6436,7 @@
         <v>-0.5305</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.2466</v>
+        <v>-1.2577</v>
       </c>
       <c r="E131" t="n">
         <v>-2.0427</v>
@@ -6476,28 +6476,28 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-2.3698</v>
+        <v>-2.2769</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.5913</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.3787</v>
+        <v>-1.351</v>
       </c>
       <c r="E132" t="n">
-        <v>-2.3698</v>
+        <v>-2.2769</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.3698</v>
+        <v>-1.2769</v>
       </c>
       <c r="G132" t="n">
         <v>-1</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.3698</v>
+        <v>-1.2769</v>
       </c>
       <c r="I132" t="n">
-        <v>-1.3826</v>
+        <v>-1.2985</v>
       </c>
       <c r="J132" t="n">
         <v>-1</v>
@@ -6509,7 +6509,7 @@
         <v>60</v>
       </c>
       <c r="M132" t="n">
-        <v>-2.3826</v>
+        <v>-2.2985</v>
       </c>
       <c r="N132" t="n">
         <v>287</v>
@@ -6528,7 +6528,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.487</v>
+        <v>-1.4948</v>
       </c>
       <c r="E133" t="n">
         <v>-2.6378</v>
@@ -6574,7 +6574,7 @@
         <v>-0.7381</v>
       </c>
       <c r="D134" t="n">
-        <v>-1.5695</v>
+        <v>-1.5762</v>
       </c>
       <c r="E134" t="n">
         <v>-2.8422</v>
@@ -6620,7 +6620,7 @@
         <v>-0.876</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.784</v>
+        <v>-1.7878</v>
       </c>
       <c r="E135" t="n">
         <v>-3.3731</v>
